--- a/ai_logs/DangHuy_AI_AUDITLOG.xlsx
+++ b/ai_logs/DangHuy_AI_AUDITLOG.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E653EC9B-A281-4BAB-8618-867C7151575C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AC597C07-B3D1-4FED-B720-7A8F967E8AB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Metadata &amp; Summary" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="239">
   <si>
     <t>AI AUDIT LOG - METADATA &amp; SUMMARY</t>
   </si>
@@ -291,18 +291,6 @@
     <t>Fabrication</t>
   </si>
   <si>
-    <t>Paper 'Smith et al. 2023' exists</t>
-  </si>
-  <si>
-    <t>Paper NOT FOUND on Google Scholar</t>
-  </si>
-  <si>
-    <t>Searched Google Scholar, ResearchGate</t>
-  </si>
-  <si>
-    <t>Used real paper 'Jones et al. 2022'</t>
-  </si>
-  <si>
     <t>HALLUCINATION TYPES REFERENCE:</t>
   </si>
   <si>
@@ -722,6 +710,57 @@
   </si>
   <si>
     <t>Code trong Eclipse IDE.</t>
+  </si>
+  <si>
+    <t>Chỉ cần ExecutorService + CountDownLatch là đủ để mô phỏng 1000 users.</t>
+  </si>
+  <si>
+    <t>Thực tế thiếu logic kiểm tra stock, retry, logging chi tiết.</t>
+  </si>
+  <si>
+    <t>Chạy simulator với 1000 threads.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Bổ sung stock validation, retry mechanism, logging để benchmark chính xác.</t>
+  </si>
+  <si>
+    <t>“NO_LOCK” có throughput cao nhất.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Throughput cao nhưng gây negative stock và inconsistency.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Benchmark với 100, 500, 1000 threads</t>
+  </si>
+  <si>
+    <t>Kết luận Optimistic Lock cân bằng hơn, bổ sung retry logic.</t>
+  </si>
+  <si>
+    <t>UML diagram với multiplicity và enum chưa chuẩn.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Multiplicity (1..*, 0..1) không đúng, thiếu enum LockType.</t>
+  </si>
+  <si>
+    <t>Đối chiếu với UML chuẩn hiện hành.</t>
+  </si>
+  <si>
+    <t>Sửa multiplicity, thêm enum LockType.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> AI đôi khi dùng cú pháp cũ, tôi phải cập nhật theo chuẩn mới.</t>
+  </si>
+  <si>
+    <t>Điều kiện if (department == "GD" || "gd") là đúng trong Java.</t>
+  </si>
+  <si>
+    <t>Sai cú pháp, không chạy được.</t>
+  </si>
+  <si>
+    <t>Compile code trong Eclipse.</t>
+  </si>
+  <si>
+    <t>Dùng equalsIgnoreCase() để xử lý input hoa/thường.</t>
   </si>
 </sst>
 </file>
@@ -731,7 +770,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -807,6 +846,19 @@
       <sz val="10"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -861,7 +913,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -898,12 +950,12 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -913,6 +965,12 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1227,7 +1285,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="19"/>
@@ -1246,7 +1304,7 @@
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -1254,7 +1312,7 @@
         <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -1262,7 +1320,7 @@
         <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -1270,7 +1328,7 @@
         <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="18" x14ac:dyDescent="0.35">
@@ -1466,7 +1524,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="20" t="s">
         <v>41</v>
       </c>
       <c r="B1" s="19"/>
@@ -1478,7 +1536,7 @@
       <c r="H1" s="19"/>
     </row>
     <row r="2" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="18" t="s">
         <v>42</v>
       </c>
       <c r="B2" s="19"/>
@@ -1607,16 +1665,16 @@
         <v>53</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1636,13 +1694,13 @@
         <v>61</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1662,13 +1720,13 @@
         <v>69</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1676,25 +1734,25 @@
         <v>7</v>
       </c>
       <c r="B10" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="F10" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="G10" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="H10" s="7" t="s">
         <v>153</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="H10" s="7" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1702,25 +1760,25 @@
         <v>8</v>
       </c>
       <c r="B11" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="F11" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="G11" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="H11" s="7" t="s">
         <v>160</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="H11" s="7" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1728,25 +1786,25 @@
         <v>9</v>
       </c>
       <c r="B12" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="F12" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="G12" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="H12" s="7" t="s">
         <v>167</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="G12" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="H12" s="7" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1754,25 +1812,25 @@
         <v>10</v>
       </c>
       <c r="B13" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="F13" s="7" t="s">
         <v>172</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="G13" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="H13" s="7" t="s">
         <v>174</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>176</v>
-      </c>
-      <c r="G13" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="H13" s="7" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1780,25 +1838,25 @@
         <v>11</v>
       </c>
       <c r="B14" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="F14" s="7" t="s">
         <v>179</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="G14" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="H14" s="7" t="s">
         <v>181</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="G14" s="7" t="s">
-        <v>184</v>
-      </c>
-      <c r="H14" s="7" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1806,25 +1864,25 @@
         <v>12</v>
       </c>
       <c r="B15" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="F15" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="G15" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="H15" s="7" t="s">
         <v>188</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="G15" s="7" t="s">
-        <v>191</v>
-      </c>
-      <c r="H15" s="7" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1832,25 +1890,25 @@
         <v>13</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="C16" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="G16" s="7" t="s">
         <v>193</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="H16" s="7" t="s">
         <v>194</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>196</v>
-      </c>
-      <c r="G16" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="H16" s="7" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1858,25 +1916,25 @@
         <v>14</v>
       </c>
       <c r="B17" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="F17" s="7" t="s">
         <v>199</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="G17" s="7" t="s">
         <v>200</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="H17" s="7" t="s">
         <v>201</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="F17" s="7" t="s">
-        <v>203</v>
-      </c>
-      <c r="G17" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="H17" s="7" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1884,25 +1942,25 @@
         <v>15</v>
       </c>
       <c r="B18" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="F18" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="G18" s="7" t="s">
         <v>207</v>
       </c>
-      <c r="D18" s="7" t="s">
+      <c r="H18" s="7" t="s">
         <v>208</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="F18" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="G18" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="H18" s="7" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1910,25 +1968,25 @@
         <v>16</v>
       </c>
       <c r="B19" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="F19" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="G19" s="7" t="s">
         <v>214</v>
       </c>
-      <c r="D19" s="7" t="s">
+      <c r="H19" s="7" t="s">
         <v>215</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="F19" s="7" t="s">
-        <v>217</v>
-      </c>
-      <c r="G19" s="7" t="s">
-        <v>218</v>
-      </c>
-      <c r="H19" s="7" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1936,25 +1994,25 @@
         <v>17</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C20" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="G20" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="D20" s="7" t="s">
+      <c r="H20" s="7" t="s">
         <v>221</v>
-      </c>
-      <c r="E20" s="7" t="s">
-        <v>222</v>
-      </c>
-      <c r="F20" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="G20" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="H20" s="7" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2078,29 +2136,27 @@
       </c>
     </row>
     <row r="4" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="7" t="s">
-        <v>65</v>
+      <c r="A4" s="7">
+        <v>7</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>82</v>
+        <v>222</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>84</v>
+        <v>223</v>
+      </c>
+      <c r="E4" s="24" t="s">
+        <v>224</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>85</v>
+        <v>225</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="7" t="s">
-        <v>31</v>
-      </c>
+      <c r="A5" s="7"/>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
       <c r="D5" s="7"/>
@@ -2108,28 +2164,64 @@
       <c r="F5" s="7"/>
     </row>
     <row r="6" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="7"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
+      <c r="A6" s="7">
+        <v>8</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="C6" s="25" t="s">
+        <v>226</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>229</v>
+      </c>
     </row>
     <row r="7" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="7"/>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
+      <c r="A7" s="7">
+        <v>10</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>234</v>
+      </c>
     </row>
     <row r="8" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
+      <c r="A8" s="7">
+        <v>15</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="9" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="7"/>
@@ -2261,18 +2353,18 @@
     </row>
     <row r="30" spans="1:6" ht="18" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="10" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -2280,54 +2372,54 @@
         <v>81</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A33" s="7" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A34" s="7" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A35" s="7" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A36" s="7" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -2351,8 +2443,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="18" t="s">
-        <v>104</v>
+      <c r="A1" s="20" t="s">
+        <v>100</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -2360,7 +2452,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="B2" s="19"/>
       <c r="C2" s="19"/>
@@ -2368,185 +2460,185 @@
     </row>
     <row r="4" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="12" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="D6" s="13"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="12" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="D7" s="13"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="12" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="D8" s="13"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="12" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="D9" s="13"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="12" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="D10" s="13"/>
     </row>
     <row r="12" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="12" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="D14" s="13"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="12" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="D15" s="13"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="12" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="D16" s="13"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="12" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="D17" s="13"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="12" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="D18" s="13"/>
     </row>
     <row r="20" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="14" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="15" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="15" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="16" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
@@ -2554,13 +2646,13 @@
         <v>43</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
